--- a/data/output/2025/evaluasi_82.xlsx
+++ b/data/output/2025/evaluasi_82.xlsx
@@ -1433,7 +1433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1549,6 +1549,398 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.186986706377651</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5759569175143009</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.181964215451849</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>35.77183544858585</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.420269925303828</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.938084602616632</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3400576350639202</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.9130764675228</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.95936152098824</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-8.605000172779055</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.596862821517361</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.776444031040787</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.3436061281103562</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8271</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Ternate</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2576073096802621</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,6 +2015,342 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.706681077693744</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.799929053481567</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>40.61884676672244</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.671186975400444</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.688590114356055</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.689548997870265</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.769459579520557</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.972386652801643</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.907852945467884</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.652665846214576</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.6890804620530149</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8272</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.4201563846099858</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1637,7 +2365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2061,6 +2789,370 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.05366611568325792</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.222952019905702</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-5.124964554070856</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>35.91183413917616</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.106548220056551</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.5107651967585241</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5.352471520691341</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.286298932952909</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6.43983202185481</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.2844822166143668</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5.022787905900593</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.1476739800956952</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.1305419641649817</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2075,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2471,6 +3563,398 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.093335437633925</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8363302417178176</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.8597820219151435</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>34.86332972448736</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4.475701804972436</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6.678609530434009</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.502982429137418</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9.271842099941454</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.821686036276237</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2.372304473799367</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.423789914019878</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6.279117780497749</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.01839062367226971</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8205</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Utara</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.201211929095804</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2485,7 +3969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2853,6 +4337,286 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.495854868063265</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.34844922397609</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>31.94624838609383</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.949703921002751</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-4.465226992753167</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>9.577387897319491</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.484640710822984</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.481059947819756</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.75675508501987</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8206</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.1449547902054994</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2867,7 +4631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3235,6 +4999,398 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.06566390159151027</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.244275152529458</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>23.15792561473297</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-8.100461855107465</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.90444594780395</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>9.22257581554492</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-5.595373923300655</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8.724221560575632</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4.163934622934614</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.233923658129217</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>16.92496083824195</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.1953808061609564</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.1397487072042184</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.07299158933575567</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3249,7 +5405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3449,6 +5605,370 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.936178619713794</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-20.78775806423622</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.700499163069136</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.889662861404285</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-6.399442728032742</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.685048845834072</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.556982248963259</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-5.875536507271949</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.865387315282486</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.206401984264198</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.6561472772688296</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.192576457282454</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8201</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Barat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.6335566793486195</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3463,7 +5983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3635,6 +6155,342 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5257359140653054</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.289654967784675</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.270740164189273</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.574468678725099</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2321424453422905</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.848660696976348</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.154756550529271</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.297957726187458</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.843867126314095</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.608554467850583</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.3700305408545861</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8203</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2523409981901545</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3649,7 +6505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3849,6 +6705,426 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.883626955809663</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.044345453108984</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-6.890645275451337</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>19.9507752390626</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.7118058234072</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.399018638352763</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.251044130035216</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.671150657653049</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.935058834146485</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.694352725345608</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.07186398446533203</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.6598487063899754</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.817620047175054</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.031760740827397</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8202</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.6798737171122936</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3863,7 +7139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3982,6 +7258,454 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.400088450302653</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2950563308052052</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.017585488775803</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>38.59231269957457</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20.85740676319352</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.623063696362556</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9.457671706031553</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.98668039719643</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.4806048264124</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.844247581939007</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.03042757749360327</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1142161716212285</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.3205504507896483</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.102334185107611</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.032279201959176</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8204</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.6804751172842119</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
